--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/16-conciliacao-de-cartao.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/16-conciliacao-de-cartao.xlsx
@@ -1368,32 +1368,32 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>COUNTIFS(Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$E$5:$E$604,"&lt;2",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)</f>
-        <v>0</v>
+        <f>COUNTIFS(Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)-COUNTIFS(Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$E$5:$E$604,"&gt;1",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)</f>
+        <v>16</v>
       </c>
       <c r="C13" s="28">
-        <f>SUMIFS(Vendas!$F$5:$F$604,Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$E$5:$E$604,"&lt;2",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)</f>
-        <v>0</v>
+        <f>SUMIFS(Vendas!$F$5:$F$604,Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)-SUMIFS(Vendas!$F$5:$F$604,Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$E$5:$E$604,"&gt;1",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)</f>
+        <v>5840</v>
       </c>
       <c r="D13" s="29">
-        <f>SUMIFS(Vendas!$I$5:$I$604,Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$E$5:$E$604,"&lt;2",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)</f>
-        <v>0</v>
+        <f>SUMIFS(Vendas!$I$5:$I$604,Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)-SUMIFS(Vendas!$I$5:$I$604,Vendas!$D$5:$D$604,"Cartão de crédito",Vendas!$E$5:$E$604,"&gt;1",Vendas!$L$5:$L$604,Config!$B$7,Vendas!$M$5:$M$604,Config!$B$5)</f>
+        <v>186.88</v>
       </c>
       <c r="E13" s="30">
         <f>IF(C13=0,"",D13/C13)</f>
-        <v/>
+        <v>0.032</v>
       </c>
       <c r="F13" s="28">
         <f>C13-D13</f>
-        <v>0</v>
+        <v>5653.12</v>
       </c>
       <c r="G13" s="31">
         <f>IF($A$5=0,"",C13/$A$5)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="32">
+        <v>0.183532369578881</v>
+      </c>
+      <c r="H13" s="32" t="str">
         <f>IF(G13="","",REPT("█",ROUND(G13*30,0)))</f>
-        <v/>
+        <v>██████</v>
       </c>
       <c r="I13" s="24" t="n"/>
       <c r="J13" s="25" t="n"/>
@@ -1443,19 +1443,19 @@
       </c>
       <c r="B15" s="33">
         <f>SUM(B11:B14)</f>
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C15" s="34">
         <f>SUM(C11:C14)</f>
-        <v>25980</v>
+        <v>31820</v>
       </c>
       <c r="D15" s="35">
         <f>SUM(D11:D14)</f>
-        <v>297.24</v>
+        <v>484.12</v>
       </c>
       <c r="F15" s="34">
         <f>SUM(F11:F14)</f>
-        <v>25682.76</v>
+        <v>31335.88</v>
       </c>
     </row>
     <row r="16">
